--- a/directory.xlsx
+++ b/directory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\prayer-partners\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F20163D-BE95-427F-AA98-3FAF10D9D870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245866F4-60D3-47D5-AC2A-FE62D50DF8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{8C5F4A37-F835-43B8-978D-074BDC2B80D7}"/>
+    <workbookView xWindow="3735" yWindow="2610" windowWidth="15450" windowHeight="9480" xr2:uid="{8C5F4A37-F835-43B8-978D-074BDC2B80D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>Last name</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>Sara6</t>
+  </si>
+  <si>
+    <t>Oof</t>
+  </si>
+  <si>
+    <t>Sara7</t>
   </si>
 </sst>
 </file>
@@ -484,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B51E398-5758-4886-AF2C-0AB770F04081}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
@@ -573,6 +579,17 @@
       </c>
       <c r="C8" s="1" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -585,6 +602,7 @@
     <hyperlink ref="C6" r:id="rId5" xr:uid="{E57FF55D-1FA1-49E4-98DF-E7895F706184}"/>
     <hyperlink ref="C7" r:id="rId6" xr:uid="{97AC64E4-6F7B-4C7E-B0DE-85B8A2C00160}"/>
     <hyperlink ref="C8" r:id="rId7" xr:uid="{0B98449A-8E0B-423D-85DD-5C529C44C855}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{4BE264F9-1A92-4C72-B14D-DD3C4F9F1A2A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
